--- a/reference/bander_portal/capture_cols.xlsx
+++ b/reference/bander_portal/capture_cols.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/hannah_vincelette_fws_gov/Documents/Documents/GitHub/landbird-dp-workflow/reference/bander_portal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{C74A7D46-3990-47F1-B9F5-960E1D601B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6952EF62-2840-4BAB-AA62-2FB2640D1342}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="8_{C74A7D46-3990-47F1-B9F5-960E1D601B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AC1412A-594B-439A-865A-FF18260AB1D2}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="-3936" windowWidth="23232" windowHeight="13992" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="capture_cols" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="136">
   <si>
     <t>BBL_template</t>
   </si>
@@ -231,12 +231,6 @@
   </si>
   <si>
     <t>Marker code color</t>
-  </si>
-  <si>
-    <t>FlagCodeIn_color</t>
-  </si>
-  <si>
-    <t>FlagCodeOut_color</t>
   </si>
   <si>
     <t>Side of Bird</t>
@@ -991,14 +985,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1036,7 +1026,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1142,7 +1132,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1284,7 +1274,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1777,7 +1767,7 @@
         <v>65</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>66</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1788,7 +1778,7 @@
         <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -1796,7 +1786,7 @@
         <v>3</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -1804,7 +1794,7 @@
         <v>3</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -1812,10 +1802,10 @@
         <v>3</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -1823,10 +1813,10 @@
         <v>3</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -1834,10 +1824,10 @@
         <v>3</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -1845,10 +1835,10 @@
         <v>3</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -1856,7 +1846,7 @@
         <v>3</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1864,10 +1854,10 @@
         <v>3</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1875,10 +1865,10 @@
         <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -1886,10 +1876,10 @@
         <v>3</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -1897,7 +1887,7 @@
         <v>3</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -1905,7 +1895,7 @@
         <v>3</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -1913,7 +1903,7 @@
         <v>3</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1921,10 +1911,10 @@
         <v>3</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -1932,7 +1922,7 @@
         <v>3</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1940,7 +1930,7 @@
         <v>3</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -1948,7 +1938,7 @@
         <v>3</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -1956,10 +1946,10 @@
         <v>3</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1967,10 +1957,10 @@
         <v>3</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1978,7 +1968,7 @@
         <v>3</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -1986,7 +1976,7 @@
         <v>3</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -1994,7 +1984,7 @@
         <v>3</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2002,7 +1992,7 @@
         <v>3</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2010,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2018,7 +2008,7 @@
         <v>3</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -2026,10 +2016,10 @@
         <v>3</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2037,10 +2027,10 @@
         <v>3</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2048,10 +2038,10 @@
         <v>3</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2059,7 +2049,7 @@
         <v>3</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -2067,7 +2057,7 @@
         <v>3</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2075,10 +2065,10 @@
         <v>3</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2086,10 +2076,10 @@
         <v>3</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2097,7 +2087,7 @@
         <v>3</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -2105,7 +2095,7 @@
         <v>3</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2113,7 +2103,7 @@
         <v>3</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,7 +2111,7 @@
         <v>3</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2129,7 +2119,7 @@
         <v>3</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2137,7 +2127,7 @@
         <v>3</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2145,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2153,23 +2143,23 @@
         <v>3</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>6</v>
@@ -2180,7 +2170,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>8</v>
@@ -2191,10 +2181,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>125</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>11</v>
@@ -2202,10 +2192,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>13</v>
@@ -2213,10 +2203,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>15</v>
@@ -2224,7 +2214,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>16</v>
@@ -2235,7 +2225,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>17</v>
@@ -2246,7 +2236,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>19</v>
@@ -2257,7 +2247,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>21</v>
@@ -2268,7 +2258,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>23</v>
@@ -2279,29 +2269,29 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>25</v>
@@ -2312,7 +2302,7 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>27</v>
@@ -2320,15 +2310,15 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>29</v>
@@ -2336,7 +2326,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>30</v>
@@ -2347,7 +2337,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>32</v>
@@ -2358,7 +2348,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>34</v>
@@ -2369,7 +2359,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>36</v>
@@ -2377,7 +2367,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>37</v>
@@ -2388,7 +2378,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>39</v>
@@ -2396,7 +2386,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>40</v>
@@ -2407,7 +2397,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>40</v>
@@ -2418,7 +2408,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>40</v>
@@ -2429,7 +2419,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>40</v>
@@ -2440,7 +2430,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>40</v>
@@ -2451,7 +2441,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>40</v>
@@ -2462,7 +2452,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>40</v>
@@ -2473,7 +2463,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>40</v>
@@ -2484,7 +2474,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>40</v>
@@ -2495,7 +2485,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>40</v>
@@ -2506,7 +2496,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>51</v>
@@ -2517,7 +2507,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>51</v>
@@ -2528,7 +2518,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>54</v>
@@ -2539,7 +2529,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>54</v>
@@ -2550,7 +2540,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>54</v>
@@ -2561,7 +2551,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>54</v>
@@ -2572,7 +2562,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>54</v>
@@ -2583,7 +2573,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>54</v>
@@ -2594,7 +2584,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>54</v>
@@ -2605,7 +2595,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>54</v>
@@ -2616,7 +2606,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>54</v>
@@ -2627,7 +2617,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>54</v>
@@ -2638,402 +2628,402 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>4</v>
@@ -3044,7 +3034,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>6</v>
@@ -3055,7 +3045,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>8</v>
@@ -3066,7 +3056,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>10</v>
@@ -3077,7 +3067,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>12</v>
@@ -3088,7 +3078,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>14</v>
@@ -3099,7 +3089,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>16</v>
@@ -3110,7 +3100,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>17</v>
@@ -3121,7 +3111,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>19</v>
@@ -3132,7 +3122,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>21</v>
@@ -3143,7 +3133,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>23</v>
@@ -3154,7 +3144,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>25</v>
@@ -3165,7 +3155,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>27</v>
@@ -3173,7 +3163,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>28</v>
@@ -3181,7 +3171,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>29</v>
@@ -3189,7 +3179,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>30</v>
@@ -3200,7 +3190,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>32</v>
@@ -3211,7 +3201,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>34</v>
@@ -3222,7 +3212,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>36</v>
@@ -3230,7 +3220,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>37</v>
@@ -3241,7 +3231,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>39</v>
@@ -3249,359 +3239,359 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>6</v>
@@ -3612,7 +3602,7 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>8</v>
@@ -3623,10 +3613,10 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>11</v>
@@ -3634,10 +3624,10 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>13</v>
@@ -3645,10 +3635,10 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>15</v>
@@ -3656,7 +3646,7 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B239" s="1" t="s">
         <v>16</v>
@@ -3667,7 +3657,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B240" s="1" t="s">
         <v>17</v>
@@ -3678,7 +3668,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B241" s="1" t="s">
         <v>19</v>
@@ -3689,7 +3679,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B242" s="1" t="s">
         <v>21</v>
@@ -3700,7 +3690,7 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B243" s="1" t="s">
         <v>23</v>
@@ -3711,29 +3701,29 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B246" s="1" t="s">
         <v>25</v>
@@ -3744,7 +3734,7 @@
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B247" s="1" t="s">
         <v>27</v>
@@ -3752,15 +3742,15 @@
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B249" s="1" t="s">
         <v>29</v>
@@ -3768,7 +3758,7 @@
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B250" s="1" t="s">
         <v>30</v>
@@ -3779,7 +3769,7 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B251" s="1" t="s">
         <v>32</v>
@@ -3790,7 +3780,7 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B252" s="1" t="s">
         <v>34</v>
@@ -3801,7 +3791,7 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B253" s="1" t="s">
         <v>36</v>
@@ -3809,7 +3799,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B254" s="1" t="s">
         <v>37</v>
@@ -3820,7 +3810,7 @@
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B255" s="1" t="s">
         <v>39</v>
@@ -3828,343 +3818,343 @@
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
